--- a/MSME/MSME_CG_Final_2Decimal.xlsx
+++ b/MSME/MSME_CG_Final_2Decimal.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9000"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="New_CG" sheetId="1" r:id="rId1"/>
     <sheet name="Disbursement_Final" sheetId="2" r:id="rId2"/>
     <sheet name="Continuity_Calculator" sheetId="3" r:id="rId3"/>
     <sheet name="NPA date" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -791,6 +792,7 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -803,7 +805,6 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1212,7 +1213,7 @@
     <col min="3" max="3" width="11.8571428571429" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="26.4285714285714" customWidth="1"/>
-    <col min="6" max="6" width="10.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="13.1428571428571" customWidth="1"/>
     <col min="7" max="7" width="13.8571428571429" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
     <col min="9" max="9" width="22.1428571428571" customWidth="1"/>
@@ -1260,24 +1261,24 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="9">
-        <v>46054</v>
-      </c>
-      <c r="B2" s="9">
-        <v>46113</v>
+      <c r="A2" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46296</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="E2">
         <f t="shared" ref="E2:E29" si="0">IF(ROW()=2,D2,E1+D2)</f>
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="F2">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="G2">
         <f t="shared" ref="G2:G29" si="1">MAX(0,E2-F2)</f>
@@ -1293,7 +1294,7 @@
       </c>
       <c r="J2">
         <f t="shared" ref="J2:J29" si="4">DATE(YEAR(B2)+IF(MONTH(B2)&gt;3,1,0),3,31)-B2+1</f>
-        <v>365</v>
+        <v>182</v>
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K29" si="5">IF(C2=2,0.5%,1.5%)</f>
@@ -1305,28 +1306,28 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="9">
-        <v>46054</v>
-      </c>
-      <c r="B3" s="9">
-        <v>46539</v>
+      <c r="A3" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B3" s="1">
+        <v>47027</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>3000000</v>
+        <v>99999999</v>
       </c>
       <c r="E3">
         <f t="shared" si="0"/>
-        <v>4000000</v>
+        <v>100299999</v>
       </c>
       <c r="F3">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="G3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50299999</v>
       </c>
       <c r="H3">
         <f t="shared" si="2"/>
@@ -1334,11 +1335,11 @@
       </c>
       <c r="I3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>50299999</v>
       </c>
       <c r="J3">
         <f t="shared" si="4"/>
-        <v>305</v>
+        <v>182</v>
       </c>
       <c r="K3">
         <f t="shared" si="5"/>
@@ -1346,14 +1347,14 @@
       </c>
       <c r="L3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>376216.43</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="9">
+      <c r="A4" s="1">
         <v>46054</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="1">
         <v>46209</v>
       </c>
       <c r="C4">
@@ -1364,22 +1365,22 @@
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="F4">
         <v>500</v>
       </c>
       <c r="G4">
         <f t="shared" si="1"/>
-        <v>3999600</v>
+        <v>100299599</v>
       </c>
       <c r="H4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>50299999</v>
       </c>
       <c r="I4">
         <f t="shared" si="3"/>
-        <v>3999600</v>
+        <v>49999600</v>
       </c>
       <c r="J4">
         <f t="shared" si="4"/>
@@ -1391,21 +1392,21 @@
       </c>
       <c r="L4">
         <f t="shared" si="6"/>
-        <v>44214.76</v>
+        <v>552735.3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G5">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H5">
         <f t="shared" si="2"/>
-        <v>3999600</v>
+        <v>100299599</v>
       </c>
       <c r="I5">
         <f t="shared" si="3"/>
@@ -1427,19 +1428,19 @@
     <row r="6" spans="1:12">
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G6">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H6">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I6">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J6">
         <f t="shared" si="4"/>
@@ -1457,19 +1458,19 @@
     <row r="7" spans="1:12">
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G7">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H7">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I7">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J7">
         <f t="shared" si="4"/>
@@ -1487,19 +1488,19 @@
     <row r="8" spans="1:12">
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H8">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I8">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J8">
         <f t="shared" si="4"/>
@@ -1517,19 +1518,19 @@
     <row r="9" spans="1:12">
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H9">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I9">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J9">
         <f t="shared" si="4"/>
@@ -1547,19 +1548,19 @@
     <row r="10" spans="1:12">
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G10">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H10">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I10">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J10">
         <f t="shared" si="4"/>
@@ -1577,19 +1578,19 @@
     <row r="11" spans="1:12">
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G11">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H11">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I11">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J11">
         <f t="shared" si="4"/>
@@ -1607,19 +1608,19 @@
     <row r="12" spans="1:12">
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H12">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I12">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J12">
         <f t="shared" si="4"/>
@@ -1637,19 +1638,19 @@
     <row r="13" spans="1:12">
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G13">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H13">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I13">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J13">
         <f t="shared" si="4"/>
@@ -1667,19 +1668,19 @@
     <row r="14" spans="1:12">
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G14">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H14">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I14">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J14">
         <f t="shared" si="4"/>
@@ -1697,19 +1698,19 @@
     <row r="15" spans="1:12">
       <c r="E15">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G15">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H15">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I15">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J15">
         <f t="shared" si="4"/>
@@ -1727,19 +1728,19 @@
     <row r="16" spans="1:12">
       <c r="E16">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G16">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H16">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I16">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J16">
         <f t="shared" si="4"/>
@@ -1757,19 +1758,19 @@
     <row r="17" spans="5:12">
       <c r="E17">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G17">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H17">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I17">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J17">
         <f t="shared" si="4"/>
@@ -1787,19 +1788,19 @@
     <row r="18" spans="5:12">
       <c r="E18">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G18">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H18">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I18">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J18">
         <f t="shared" si="4"/>
@@ -1817,19 +1818,19 @@
     <row r="19" spans="5:12">
       <c r="E19">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G19">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H19">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I19">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J19">
         <f t="shared" si="4"/>
@@ -1847,19 +1848,19 @@
     <row r="20" spans="5:12">
       <c r="E20">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G20">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H20">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I20">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J20">
         <f t="shared" si="4"/>
@@ -1877,19 +1878,19 @@
     <row r="21" spans="5:12">
       <c r="E21">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G21">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H21">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I21">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J21">
         <f t="shared" si="4"/>
@@ -1907,19 +1908,19 @@
     <row r="22" spans="5:12">
       <c r="E22">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G22">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H22">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I22">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J22">
         <f t="shared" si="4"/>
@@ -1937,19 +1938,19 @@
     <row r="23" spans="5:12">
       <c r="E23">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G23">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H23">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I23">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J23">
         <f t="shared" si="4"/>
@@ -1967,19 +1968,19 @@
     <row r="24" spans="5:12">
       <c r="E24">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G24">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H24">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I24">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J24">
         <f t="shared" si="4"/>
@@ -1997,19 +1998,19 @@
     <row r="25" spans="5:12">
       <c r="E25">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G25">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H25">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I25">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J25">
         <f t="shared" si="4"/>
@@ -2027,19 +2028,19 @@
     <row r="26" spans="5:12">
       <c r="E26">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G26">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H26">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I26">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J26">
         <f t="shared" si="4"/>
@@ -2057,19 +2058,19 @@
     <row r="27" spans="5:12">
       <c r="E27">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G27">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H27">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I27">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J27">
         <f t="shared" si="4"/>
@@ -2087,19 +2088,19 @@
     <row r="28" spans="5:12">
       <c r="E28">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G28">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H28">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I28">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J28">
         <f t="shared" si="4"/>
@@ -2117,19 +2118,19 @@
     <row r="29" spans="5:12">
       <c r="E29">
         <f t="shared" si="0"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="G29">
         <f t="shared" si="1"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="H29">
         <f t="shared" si="2"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="I29">
         <f t="shared" si="3"/>
-        <v>4000100</v>
+        <v>100300099</v>
       </c>
       <c r="J29">
         <f t="shared" si="4"/>
@@ -2156,236 +2157,236 @@
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="14.1428571428571" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1428571428571" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.7142857142857" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.8571428571429" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.1428571428571" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.8571428571429" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.1428571428571" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.8571428571429" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1428571428571" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.8571428571429" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.4285714285714" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1428571428571" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.1428571428571" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.7142857142857" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.8571428571429" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.1428571428571" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.8571428571429" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.1428571428571" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.8571428571429" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.1428571428571" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16.8571428571429" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.4285714285714" style="2" customWidth="1"/>
     <col min="12" max="12" width="6.57142857142857" customWidth="1"/>
     <col min="13" max="13" width="30.4285714285714" customWidth="1"/>
     <col min="14" max="14" width="18.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" spans="1:13">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="5" customFormat="1" spans="1:13">
+      <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="6">
+      <c r="A2" s="7">
         <v>45748</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <v>47211</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>1</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="8">
         <v>1000012.79</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="8">
         <v>1001.79</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="2">
         <v>500</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="2">
         <f>F2+G2</f>
         <v>1001014.58</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <f>I2-H2</f>
         <v>1000514.58</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="2">
         <v>4</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="2">
         <f>IF(E2=1,IF(K2&lt;=3,0.015,0.01),0.005)</f>
         <v>0.01</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="2">
         <f>IF(AND(C2="NPA",D2="STANDARD"),J2*L2*2,IF(D2="STANDARD",J2*L2,0))</f>
         <v>10005.1458</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="6">
+      <c r="A3" s="7">
         <v>45748</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <v>47211</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>1</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="9">
         <v>1000043.02</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="9">
         <v>100043.02</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="2">
         <v>500</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="2">
         <f>F3+G3</f>
         <v>1100086.04</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="2">
         <f>I3-H3</f>
         <v>1099586.04</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="2">
         <v>4</v>
       </c>
-      <c r="L3" s="1">
+      <c r="L3" s="2">
         <f>IF(E3=1,IF(K3&lt;=3,0.015,0.01),0.005)</f>
         <v>0.01</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3" s="2">
         <f>IF(AND(C3="NPA",D3="STANDARD"),J3*L3*2,IF(D3="STANDARD",J3*L3,0))</f>
         <v>10995.8604</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>45748</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>47211</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>2</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="9">
         <v>200300.33</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="9">
         <v>200200.33</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="2">
         <v>500</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="2">
         <f>F4+G4</f>
         <v>400500.66</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="2">
         <f>I4-H4</f>
         <v>400000.66</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="2">
         <v>4</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4" s="2">
         <f>IF(E4=1,IF(K4&lt;=3,0.015,0.01),0.005)</f>
         <v>0.005</v>
       </c>
-      <c r="M4" s="1">
+      <c r="M4" s="2">
         <f>IF(AND(C4="NPA",D4="STANDARD"),J4*L4*2,IF(D4="STANDARD",J4*L4,0))</f>
         <v>2000.0033</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>45748</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>47211</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>2</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="9">
         <v>20010.65</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="9">
         <v>20300.65</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="2">
         <v>500</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="2">
         <f>F5+G5</f>
         <v>40311.3</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="2">
         <f>I5-H5</f>
         <v>39811.3</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5" s="2">
         <f>IF(E5=1,IF(K5&lt;=3,0.015,0.01),0.005)</f>
         <v>0.005</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5" s="2">
         <f>IF(AND(C5="NPA",D5="STANDARD"),J5*L5*2,IF(D5="STANDARD",J5*L5,0))</f>
         <v>199.0565</v>
       </c>
@@ -2402,81 +2403,109 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="17.4285714285714" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5714285714286" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.4285714285714" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.7142857142857" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5714285714286" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.8571428571429" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.2857142857143" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.8571428571429" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="17.4285714285714" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.5714285714286" style="2" customWidth="1"/>
+    <col min="4" max="4" width="29.4285714285714" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.7142857142857" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.5714285714286" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.8571428571429" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.2857142857143" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.8571428571429" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="2" customFormat="1" spans="1:9">
+      <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:9">
-      <c r="A2" s="3">
+    <row r="2" s="2" customFormat="1" spans="1:9">
+      <c r="A2" s="4">
         <v>46853</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <f>DATE(YEAR(A2)-(MONTH(A2)&lt;4),3,31)</f>
         <v>46843</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>46783</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="4">
         <f>A2-180</f>
         <v>46673</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="4">
         <f>DATE(YEAR(A2)-1-(MONTH(A2)&lt;4),4,1)</f>
         <v>46478</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="4">
         <f>MAX(D2,E2)</f>
         <v>46673</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="4">
         <f>B2</f>
         <v>46843</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="3">
         <f>A2-C2</f>
         <v>70</v>
       </c>
-      <c r="I2" s="2" t="str">
+      <c r="I2" s="3" t="str">
         <f>IF(AND(C2&gt;=F2,C2&lt;=G2),"Valid","Invalid")</f>
         <v>Valid</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="13.2857142857143" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1">
+        <v>47027</v>
+      </c>
+      <c r="B1" s="1">
+        <v>47208</v>
+      </c>
+      <c r="D1">
+        <f>B1-A1</f>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/MSME/MSME_CG_Final_2Decimal.xlsx
+++ b/MSME/MSME_CG_Final_2Decimal.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9600" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="New_CG" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="Continuity_Calculator" sheetId="3" r:id="rId3"/>
     <sheet name="NPA date" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
+    <sheet name="Dist" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="107">
   <si>
     <t>Sanction Amount</t>
   </si>
@@ -127,26 +128,264 @@
   </si>
   <si>
     <t>Validation</t>
+  </si>
+  <si>
+    <t>CGPAN</t>
+  </si>
+  <si>
+    <t>LoanAccountNumber</t>
+  </si>
+  <si>
+    <t>DisbursementAmount</t>
+  </si>
+  <si>
+    <t>DisbursementDate</t>
+  </si>
+  <si>
+    <t>CGFees</t>
+  </si>
+  <si>
+    <t>IGST</t>
+  </si>
+  <si>
+    <t>CGST</t>
+  </si>
+  <si>
+    <t>SGST</t>
+  </si>
+  <si>
+    <t>MSME</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>PartialCollateralSecurityAmount</t>
+  </si>
+  <si>
+    <t>Net AMT</t>
+  </si>
+  <si>
+    <t>FY end</t>
+  </si>
+  <si>
+    <t>CF fee</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357114</t>
+  </si>
+  <si>
+    <t>QAMSME20</t>
+  </si>
+  <si>
+    <t>179989100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357115</t>
+  </si>
+  <si>
+    <t>QAMSME19</t>
+  </si>
+  <si>
+    <t>99979100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357116</t>
+  </si>
+  <si>
+    <t>QAMSME18</t>
+  </si>
+  <si>
+    <t>999969100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357117</t>
+  </si>
+  <si>
+    <t>QAMSME17</t>
+  </si>
+  <si>
+    <t>999959100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357118</t>
+  </si>
+  <si>
+    <t>QAMSME16</t>
+  </si>
+  <si>
+    <t>199949100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357119</t>
+  </si>
+  <si>
+    <t>QAMSME15</t>
+  </si>
+  <si>
+    <t>99939100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357120</t>
+  </si>
+  <si>
+    <t>QAMSME14</t>
+  </si>
+  <si>
+    <t>999929100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357121</t>
+  </si>
+  <si>
+    <t>QAMSME13</t>
+  </si>
+  <si>
+    <t>999919100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357122</t>
+  </si>
+  <si>
+    <t>QAMSME12</t>
+  </si>
+  <si>
+    <t>199909100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357123</t>
+  </si>
+  <si>
+    <t>QAMSME11</t>
+  </si>
+  <si>
+    <t>199899100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357124</t>
+  </si>
+  <si>
+    <t>QAMSME10</t>
+  </si>
+  <si>
+    <t>999889100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357125</t>
+  </si>
+  <si>
+    <t>QAMSME09</t>
+  </si>
+  <si>
+    <t>999879100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357126</t>
+  </si>
+  <si>
+    <t>QAMSME08</t>
+  </si>
+  <si>
+    <t>149869100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357127</t>
+  </si>
+  <si>
+    <t>QAMSME07</t>
+  </si>
+  <si>
+    <t>179859100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357128</t>
+  </si>
+  <si>
+    <t>QAMSME06</t>
+  </si>
+  <si>
+    <t>999849100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357129</t>
+  </si>
+  <si>
+    <t>QAMSME05</t>
+  </si>
+  <si>
+    <t>999839100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357130</t>
+  </si>
+  <si>
+    <t>QAMSME04</t>
+  </si>
+  <si>
+    <t>99829100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357131</t>
+  </si>
+  <si>
+    <t>QAMSME03</t>
+  </si>
+  <si>
+    <t>199819100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357132</t>
+  </si>
+  <si>
+    <t>QAMSME02</t>
+  </si>
+  <si>
+    <t>999809100</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357133</t>
+  </si>
+  <si>
+    <t>QAMSME01</t>
+  </si>
+  <si>
+    <t>999799100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="181" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -307,12 +546,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -660,151 +905,159 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -857,6 +1110,20 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="181" formatCode="0_ "/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -864,6 +1131,39 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:P21" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P21" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="CGPAN"/>
+    <tableColumn id="2" name="LoanAccountNumber"/>
+    <tableColumn id="3" name="DisbursementAmount"/>
+    <tableColumn id="4" name="DisbursementDate"/>
+    <tableColumn id="5" name="CGFees"/>
+    <tableColumn id="6" name="IGST"/>
+    <tableColumn id="7" name="CGST"/>
+    <tableColumn id="8" name="SGST"/>
+    <tableColumn id="9" name="MSME"/>
+    <tableColumn id="10" name="D1"/>
+    <tableColumn id="11" name="PartialCollateralSecurityAmount"/>
+    <tableColumn id="12" name="Net AMT" dataDxfId="0">
+      <calculatedColumnFormula>J2+C2-K2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" name="FY end"/>
+    <tableColumn id="14" name="Days" dataDxfId="1">
+      <calculatedColumnFormula>M2-D2+1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" name="CF fee" dataDxfId="2">
+      <calculatedColumnFormula>IF(I2=2,L2*0.5%*N2/365,L2*1.5%*N2/365)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" name="Column1" dataDxfId="3">
+      <calculatedColumnFormula>E2-O2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1261,10 +1561,10 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1">
+      <c r="A2" s="7">
         <v>46199</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="7">
         <v>46296</v>
       </c>
       <c r="C2">
@@ -1306,10 +1606,10 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1">
+      <c r="A3" s="7">
         <v>46199</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="7">
         <v>47027</v>
       </c>
       <c r="C3">
@@ -1351,10 +1651,10 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1">
+      <c r="A4" s="7">
         <v>46054</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="7">
         <v>46209</v>
       </c>
       <c r="C4">
@@ -2157,236 +2457,236 @@
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="14.1428571428571" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.1428571428571" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.7142857142857" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.8571428571429" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.1428571428571" style="2" customWidth="1"/>
-    <col min="6" max="6" width="21.8571428571429" style="2" customWidth="1"/>
-    <col min="7" max="7" width="21.1428571428571" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.8571428571429" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.1428571428571" style="2" customWidth="1"/>
-    <col min="10" max="10" width="16.8571428571429" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.4285714285714" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14.1428571428571" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.1428571428571" style="8" customWidth="1"/>
+    <col min="3" max="3" width="26.7142857142857" style="8" customWidth="1"/>
+    <col min="4" max="4" width="21.8571428571429" style="8" customWidth="1"/>
+    <col min="5" max="5" width="21.1428571428571" style="8" customWidth="1"/>
+    <col min="6" max="6" width="21.8571428571429" style="8" customWidth="1"/>
+    <col min="7" max="7" width="21.1428571428571" style="8" customWidth="1"/>
+    <col min="8" max="8" width="13.8571428571429" style="8" customWidth="1"/>
+    <col min="9" max="9" width="15.1428571428571" style="8" customWidth="1"/>
+    <col min="10" max="10" width="16.8571428571429" style="8" customWidth="1"/>
+    <col min="11" max="11" width="13.4285714285714" style="8" customWidth="1"/>
     <col min="12" max="12" width="6.57142857142857" customWidth="1"/>
     <col min="13" max="13" width="30.4285714285714" customWidth="1"/>
     <col min="14" max="14" width="18.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1" spans="1:13">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="11" customFormat="1" spans="1:13">
+      <c r="A1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="12" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="7">
+      <c r="A2" s="13">
         <v>45748</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="13">
         <v>47211</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="8">
         <v>1</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="14">
         <v>1000012.79</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="14">
         <v>1001.79</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="8">
         <v>500</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="8">
         <f>F2+G2</f>
         <v>1001014.58</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="8">
         <f>I2-H2</f>
         <v>1000514.58</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="8">
         <v>4</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="8">
         <f>IF(E2=1,IF(K2&lt;=3,0.015,0.01),0.005)</f>
         <v>0.01</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="8">
         <f>IF(AND(C2="NPA",D2="STANDARD"),J2*L2*2,IF(D2="STANDARD",J2*L2,0))</f>
         <v>10005.1458</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="7">
+      <c r="A3" s="13">
         <v>45748</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="13">
         <v>47211</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="8">
         <v>1</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="15">
         <v>1000043.02</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="15">
         <v>100043.02</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="8">
         <v>500</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="8">
         <f>F3+G3</f>
         <v>1100086.04</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="8">
         <f>I3-H3</f>
         <v>1099586.04</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="8">
         <v>4</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="8">
         <f>IF(E3=1,IF(K3&lt;=3,0.015,0.01),0.005)</f>
         <v>0.01</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="8">
         <f>IF(AND(C3="NPA",D3="STANDARD"),J3*L3*2,IF(D3="STANDARD",J3*L3,0))</f>
         <v>10995.8604</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="7">
+      <c r="A4" s="13">
         <v>45748</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="13">
         <v>47211</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="8">
         <v>2</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="15">
         <v>200300.33</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="15">
         <v>200200.33</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="8">
         <v>500</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="8">
         <f>F4+G4</f>
         <v>400500.66</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="8">
         <f>I4-H4</f>
         <v>400000.66</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="8">
         <v>4</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="8">
         <f>IF(E4=1,IF(K4&lt;=3,0.015,0.01),0.005)</f>
         <v>0.005</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4" s="8">
         <f>IF(AND(C4="NPA",D4="STANDARD"),J4*L4*2,IF(D4="STANDARD",J4*L4,0))</f>
         <v>2000.0033</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="7">
+      <c r="A5" s="13">
         <v>45748</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="13">
         <v>47211</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="8">
         <v>2</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="15">
         <v>20010.65</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="15">
         <v>20300.65</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="8">
         <v>500</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="8">
         <f>F5+G5</f>
         <v>40311.3</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="8">
         <f>I5-H5</f>
         <v>39811.3</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="8">
         <f>IF(E5=1,IF(K5&lt;=3,0.015,0.01),0.005)</f>
         <v>0.005</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="8">
         <f>IF(AND(C5="NPA",D5="STANDARD"),J5*L5*2,IF(D5="STANDARD",J5*L5,0))</f>
         <v>199.0565</v>
       </c>
@@ -2403,79 +2703,79 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="17.4285714285714" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.5714285714286" style="2" customWidth="1"/>
-    <col min="4" max="4" width="29.4285714285714" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.7142857142857" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.5714285714286" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19.8571428571429" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.2857142857143" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.8571428571429" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="17.4285714285714" style="8" customWidth="1"/>
+    <col min="2" max="2" width="18" style="8" customWidth="1"/>
+    <col min="3" max="3" width="15.5714285714286" style="8" customWidth="1"/>
+    <col min="4" max="4" width="29.4285714285714" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17.7142857142857" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.5714285714286" style="8" customWidth="1"/>
+    <col min="7" max="7" width="19.8571428571429" style="8" customWidth="1"/>
+    <col min="8" max="8" width="16.2857142857143" style="8" customWidth="1"/>
+    <col min="9" max="9" width="10.8571428571429" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" spans="1:9">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="8" customFormat="1" spans="1:9">
+      <c r="A1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:9">
-      <c r="A2" s="4">
+    <row r="2" s="8" customFormat="1" spans="1:9">
+      <c r="A2" s="10">
         <v>46853</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="10">
         <f>DATE(YEAR(A2)-(MONTH(A2)&lt;4),3,31)</f>
         <v>46843</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="10">
         <v>46783</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="10">
         <f>A2-180</f>
         <v>46673</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="10">
         <f>DATE(YEAR(A2)-1-(MONTH(A2)&lt;4),4,1)</f>
         <v>46478</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="10">
         <f>MAX(D2,E2)</f>
         <v>46673</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="10">
         <f>B2</f>
         <v>46843</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="9">
         <f>A2-C2</f>
         <v>70</v>
       </c>
-      <c r="I2" s="3" t="str">
+      <c r="I2" s="9" t="str">
         <f>IF(AND(C2&gt;=F2,C2&lt;=G2),"Valid","Invalid")</f>
         <v>Valid</v>
       </c>
@@ -2497,10 +2797,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1">
+      <c r="A1" s="7">
         <v>47027</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B1" s="7">
         <v>47208</v>
       </c>
       <c r="D1">
@@ -2512,4 +2812,1158 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P21"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="16.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="15.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="24.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="17.2857142857143" customWidth="1"/>
+    <col min="12" max="12" width="11.7142857142857"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="16" width="13.4285714285714" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E2" s="1">
+        <v>324107.34</v>
+      </c>
+      <c r="F2" s="1">
+        <v>58339.32</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>2</v>
+      </c>
+      <c r="J2" s="4">
+        <v>10000</v>
+      </c>
+      <c r="K2" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L2" s="5">
+        <f t="shared" ref="L2:L21" si="0">J2+C2-K2</f>
+        <v>129999100</v>
+      </c>
+      <c r="M2" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N2" s="5">
+        <f t="shared" ref="N2:N21" si="1">M2-D2+1</f>
+        <v>182</v>
+      </c>
+      <c r="O2" s="5">
+        <f t="shared" ref="O2:O21" si="2">IF(I2=2,L2*0.5%*N2/365,L2*1.5%*N2/365)</f>
+        <v>324107.345205479</v>
+      </c>
+      <c r="P2" s="6">
+        <f t="shared" ref="P2:P21" si="3">E2-O2</f>
+        <v>-0.00520547945052385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E3" s="1">
+        <v>124655.29</v>
+      </c>
+      <c r="F3" s="1">
+        <v>22437.95</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>2</v>
+      </c>
+      <c r="J3" s="4">
+        <v>20000</v>
+      </c>
+      <c r="K3" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L3" s="5">
+        <f t="shared" si="0"/>
+        <v>49999100</v>
+      </c>
+      <c r="M3" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N3" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O3" s="5">
+        <f t="shared" si="2"/>
+        <v>124655.290410959</v>
+      </c>
+      <c r="P3" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.000410958906286396</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E4" s="1">
+        <v>7105472.62</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1278985.07</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4">
+        <v>30000</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L4" s="5">
+        <f t="shared" si="0"/>
+        <v>949999100</v>
+      </c>
+      <c r="M4" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N4" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O4" s="5">
+        <f t="shared" si="2"/>
+        <v>7105472.72054795</v>
+      </c>
+      <c r="P4" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.100547945126891</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E5" s="1">
+        <v>7105472.62</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1278985.07</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4">
+        <v>40000</v>
+      </c>
+      <c r="K5" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L5" s="5">
+        <f t="shared" si="0"/>
+        <v>949999100</v>
+      </c>
+      <c r="M5" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N5" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O5" s="5">
+        <f t="shared" si="2"/>
+        <v>7105472.72054795</v>
+      </c>
+      <c r="P5" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.100547945126891</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>2</v>
+      </c>
+      <c r="J6" s="4">
+        <v>50000</v>
+      </c>
+      <c r="K6" s="1">
+        <v>450000000</v>
+      </c>
+      <c r="L6" s="5">
+        <f t="shared" si="0"/>
+        <v>-250000900</v>
+      </c>
+      <c r="M6" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N6" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O6" s="5">
+        <f t="shared" si="2"/>
+        <v>-623289.915068493</v>
+      </c>
+      <c r="P6" s="6">
+        <f t="shared" si="3"/>
+        <v>623289.915068493</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>2</v>
+      </c>
+      <c r="J7" s="4">
+        <v>60000</v>
+      </c>
+      <c r="K7" s="1">
+        <v>450000000</v>
+      </c>
+      <c r="L7" s="5">
+        <f t="shared" si="0"/>
+        <v>-350000900</v>
+      </c>
+      <c r="M7" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N7" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O7" s="5">
+        <f t="shared" si="2"/>
+        <v>-872604.983561644</v>
+      </c>
+      <c r="P7" s="6">
+        <f t="shared" si="3"/>
+        <v>872604.983561644</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7105472.62</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1278985.07</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4">
+        <v>70000</v>
+      </c>
+      <c r="K8" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L8" s="5">
+        <f t="shared" si="0"/>
+        <v>949999100</v>
+      </c>
+      <c r="M8" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N8" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O8" s="5">
+        <f t="shared" si="2"/>
+        <v>7105472.72054795</v>
+      </c>
+      <c r="P8" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.100547945126891</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E9" s="1">
+        <v>7105472.62</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1278985.07</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4">
+        <v>80000</v>
+      </c>
+      <c r="K9" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L9" s="5">
+        <f t="shared" si="0"/>
+        <v>949999100</v>
+      </c>
+      <c r="M9" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N9" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O9" s="5">
+        <f t="shared" si="2"/>
+        <v>7105472.72054795</v>
+      </c>
+      <c r="P9" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.100547945126891</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E10" s="1">
+        <v>373970.35</v>
+      </c>
+      <c r="F10" s="1">
+        <v>67314.66</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2</v>
+      </c>
+      <c r="J10" s="4">
+        <v>90000</v>
+      </c>
+      <c r="K10" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" si="0"/>
+        <v>149999100</v>
+      </c>
+      <c r="M10" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N10" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O10" s="5">
+        <f t="shared" si="2"/>
+        <v>373970.35890411</v>
+      </c>
+      <c r="P10" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.0089041095925495</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E11" s="1">
+        <v>373970.35</v>
+      </c>
+      <c r="F11" s="1">
+        <v>67314.66</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4">
+        <v>100000</v>
+      </c>
+      <c r="K11" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="0"/>
+        <v>149999100</v>
+      </c>
+      <c r="M11" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N11" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O11" s="5">
+        <f t="shared" si="2"/>
+        <v>373970.35890411</v>
+      </c>
+      <c r="P11" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.0089041095925495</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E12" s="1">
+        <v>7105472.62</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1278985.07</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4">
+        <v>110000</v>
+      </c>
+      <c r="K12" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="0"/>
+        <v>949999100</v>
+      </c>
+      <c r="M12" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N12" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O12" s="5">
+        <f t="shared" si="2"/>
+        <v>7105472.72054795</v>
+      </c>
+      <c r="P12" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.100547945126891</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4113691.84</v>
+      </c>
+      <c r="F13" s="1">
+        <v>740464.53</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <v>120000</v>
+      </c>
+      <c r="K13" s="1">
+        <v>450000000</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="0"/>
+        <v>549999100</v>
+      </c>
+      <c r="M13" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N13" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O13" s="5">
+        <f t="shared" si="2"/>
+        <v>4113691.89863014</v>
+      </c>
+      <c r="P13" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.0586301372386515</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2</v>
+      </c>
+      <c r="J14" s="4">
+        <v>130000</v>
+      </c>
+      <c r="K14" s="1">
+        <v>450000000</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="0"/>
+        <v>-300000900</v>
+      </c>
+      <c r="M14" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N14" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O14" s="5">
+        <f t="shared" si="2"/>
+        <v>-747947.449315069</v>
+      </c>
+      <c r="P14" s="6">
+        <f t="shared" si="3"/>
+        <v>747947.449315069</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E15" s="1">
+        <v>324107.34</v>
+      </c>
+      <c r="F15" s="1">
+        <v>58339.32</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2</v>
+      </c>
+      <c r="J15" s="4">
+        <v>140000</v>
+      </c>
+      <c r="K15" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="0"/>
+        <v>129999100</v>
+      </c>
+      <c r="M15" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N15" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O15" s="5">
+        <f t="shared" si="2"/>
+        <v>324107.345205479</v>
+      </c>
+      <c r="P15" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.00520547945052385</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E16" s="1">
+        <v>7105472.62</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1278985.07</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1</v>
+      </c>
+      <c r="J16" s="4">
+        <v>150000</v>
+      </c>
+      <c r="K16" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="0"/>
+        <v>949999100</v>
+      </c>
+      <c r="M16" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N16" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O16" s="5">
+        <f t="shared" si="2"/>
+        <v>7105472.72054795</v>
+      </c>
+      <c r="P16" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.100547945126891</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E17" s="1">
+        <v>7105472.62</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1278985.07</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4">
+        <v>160000</v>
+      </c>
+      <c r="K17" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="0"/>
+        <v>949999100</v>
+      </c>
+      <c r="M17" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N17" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O17" s="5">
+        <f t="shared" si="2"/>
+        <v>7105472.72054795</v>
+      </c>
+      <c r="P17" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.100547945126891</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E18" s="1">
+        <v>124655.29</v>
+      </c>
+      <c r="F18" s="1">
+        <v>22437.95</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2</v>
+      </c>
+      <c r="J18" s="4">
+        <v>170000</v>
+      </c>
+      <c r="K18" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="0"/>
+        <v>49999100</v>
+      </c>
+      <c r="M18" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N18" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O18" s="5">
+        <f t="shared" si="2"/>
+        <v>124655.290410959</v>
+      </c>
+      <c r="P18" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.000410958906286396</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E19" s="1">
+        <v>373970.35</v>
+      </c>
+      <c r="F19" s="1">
+        <v>67314.66</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>2</v>
+      </c>
+      <c r="J19" s="4">
+        <v>180000</v>
+      </c>
+      <c r="K19" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="0"/>
+        <v>149999100</v>
+      </c>
+      <c r="M19" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N19" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O19" s="5">
+        <f t="shared" si="2"/>
+        <v>373970.35890411</v>
+      </c>
+      <c r="P19" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.0089041095925495</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E20" s="1">
+        <v>4113691.84</v>
+      </c>
+      <c r="F20" s="1">
+        <v>740464.53</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1</v>
+      </c>
+      <c r="J20" s="4">
+        <v>190000</v>
+      </c>
+      <c r="K20" s="1">
+        <v>450000000</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="0"/>
+        <v>549999100</v>
+      </c>
+      <c r="M20" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N20" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O20" s="5">
+        <f t="shared" si="2"/>
+        <v>4113691.89863014</v>
+      </c>
+      <c r="P20" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.0586301372386515</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="2">
+        <v>47027</v>
+      </c>
+      <c r="E21" s="1">
+        <v>4113691.84</v>
+      </c>
+      <c r="F21" s="1">
+        <v>740464.53</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1</v>
+      </c>
+      <c r="J21" s="4">
+        <v>200000</v>
+      </c>
+      <c r="K21" s="1">
+        <v>450000000</v>
+      </c>
+      <c r="L21" s="5">
+        <f t="shared" si="0"/>
+        <v>549999100</v>
+      </c>
+      <c r="M21" s="2">
+        <v>47208</v>
+      </c>
+      <c r="N21" s="5">
+        <f t="shared" si="1"/>
+        <v>182</v>
+      </c>
+      <c r="O21" s="5">
+        <f t="shared" si="2"/>
+        <v>4113691.89863014</v>
+      </c>
+      <c r="P21" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.0586301372386515</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/MSME/MSME_CG_Final_2Decimal.xlsx
+++ b/MSME/MSME_CG_Final_2Decimal.xlsx
@@ -1,18 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" activeTab="5"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="New_CG" sheetId="1" r:id="rId1"/>
     <sheet name="Disbursement_Final" sheetId="2" r:id="rId2"/>
     <sheet name="Continuity_Calculator" sheetId="3" r:id="rId3"/>
     <sheet name="NPA date" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
-    <sheet name="Dist" sheetId="6" r:id="rId6"/>
+    <sheet name="Dist" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="115">
   <si>
     <t>Sanction Amount</t>
   </si>
@@ -79,30 +78,66 @@
     <t>CG Fee</t>
   </si>
   <si>
+    <t>CGPAN</t>
+  </si>
+  <si>
+    <t>Loan Account Number</t>
+  </si>
+  <si>
     <t>Continuity Date</t>
   </si>
   <si>
-    <t>Prev Status</t>
-  </si>
-  <si>
     <t>Current Status</t>
   </si>
   <si>
-    <t>Principal Outstanding</t>
-  </si>
-  <si>
-    <t>Interest Outstanding</t>
-  </si>
-  <si>
-    <t>Total Exposure</t>
+    <t>Principal O/S</t>
+  </si>
+  <si>
+    <t>Interest O/S</t>
   </si>
   <si>
     <t>Loan Year</t>
   </si>
   <si>
+    <t>Missed Continuity Years</t>
+  </si>
+  <si>
+    <t>Current FY CG Fee</t>
+  </si>
+  <si>
+    <t>Missed FY CG Fee</t>
+  </si>
+  <si>
+    <t>Total CG Fee Payable</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357114</t>
+  </si>
+  <si>
+    <t>loan01</t>
+  </si>
+  <si>
+    <t>26-06-2026</t>
+  </si>
+  <si>
+    <t>01-04-2029</t>
+  </si>
+  <si>
     <t>STANDARD</t>
   </si>
   <si>
+    <t>CGMSMGEN2109202600357116</t>
+  </si>
+  <si>
+    <t>loan02</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357117</t>
+  </si>
+  <si>
+    <t>loan03</t>
+  </si>
+  <si>
     <t>Upload Date</t>
   </si>
   <si>
@@ -130,9 +165,6 @@
     <t>Validation</t>
   </si>
   <si>
-    <t>CGPAN</t>
-  </si>
-  <si>
     <t>LoanAccountNumber</t>
   </si>
   <si>
@@ -175,9 +207,6 @@
     <t>Column1</t>
   </si>
   <si>
-    <t>CGMSMGEN2109202600357114</t>
-  </si>
-  <si>
     <t>QAMSME20</t>
   </si>
   <si>
@@ -193,16 +222,10 @@
     <t>99979100</t>
   </si>
   <si>
-    <t>CGMSMGEN2109202600357116</t>
-  </si>
-  <si>
     <t>QAMSME18</t>
   </si>
   <si>
     <t>999969100</t>
-  </si>
-  <si>
-    <t>CGMSMGEN2109202600357117</t>
   </si>
   <si>
     <t>QAMSME17</t>
@@ -367,7 +390,7 @@
     <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="181" formatCode="0_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,6 +412,21 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -546,7 +584,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -561,7 +599,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FF1F4E78"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,6 +642,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -746,7 +790,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -766,15 +810,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -905,137 +940,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
@@ -1045,19 +1080,22 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
     <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1450,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
@@ -1504,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:L29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -1561,10 +1599,10 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="7">
+      <c r="A2" s="18">
         <v>46199</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="18">
         <v>46296</v>
       </c>
       <c r="C2">
@@ -1606,10 +1644,10 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="7">
+      <c r="A3" s="18">
         <v>46199</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="18">
         <v>47027</v>
       </c>
       <c r="C3">
@@ -1651,10 +1689,10 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="7">
+      <c r="A4" s="18">
         <v>46054</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="18">
         <v>46209</v>
       </c>
       <c r="C4">
@@ -2453,245 +2491,255 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:P4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="14.1428571428571" style="8" customWidth="1"/>
-    <col min="2" max="2" width="16.1428571428571" style="8" customWidth="1"/>
-    <col min="3" max="3" width="26.7142857142857" style="8" customWidth="1"/>
-    <col min="4" max="4" width="21.8571428571429" style="8" customWidth="1"/>
-    <col min="5" max="5" width="21.1428571428571" style="8" customWidth="1"/>
-    <col min="6" max="6" width="21.8571428571429" style="8" customWidth="1"/>
-    <col min="7" max="7" width="21.1428571428571" style="8" customWidth="1"/>
-    <col min="8" max="8" width="13.8571428571429" style="8" customWidth="1"/>
-    <col min="9" max="9" width="15.1428571428571" style="8" customWidth="1"/>
-    <col min="10" max="10" width="16.8571428571429" style="8" customWidth="1"/>
-    <col min="11" max="11" width="13.4285714285714" style="8" customWidth="1"/>
-    <col min="12" max="12" width="6.57142857142857" customWidth="1"/>
+    <col min="1" max="1" width="14.1428571428571" style="7" customWidth="1"/>
+    <col min="2" max="2" width="18.1428571428571" style="7" customWidth="1"/>
+    <col min="3" max="3" width="26.7142857142857" style="7" customWidth="1"/>
+    <col min="4" max="4" width="21.8571428571429" style="7" customWidth="1"/>
+    <col min="5" max="5" width="21.1428571428571" style="7" customWidth="1"/>
+    <col min="6" max="6" width="21.8571428571429" style="7" customWidth="1"/>
+    <col min="7" max="7" width="21.1428571428571" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.8571428571429" style="7" customWidth="1"/>
+    <col min="9" max="9" width="15.1428571428571" style="7" customWidth="1"/>
+    <col min="10" max="10" width="16.8571428571429" style="7" customWidth="1"/>
+    <col min="11" max="11" width="13.4285714285714" style="7" customWidth="1"/>
+    <col min="12" max="12" width="14.5714285714286" customWidth="1"/>
     <col min="13" max="13" width="30.4285714285714" customWidth="1"/>
     <col min="14" max="14" width="18.2857142857143" customWidth="1"/>
+    <col min="15" max="15" width="13.4285714285714" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="11" customFormat="1" spans="1:13">
-      <c r="A1" s="12" t="s">
+    <row r="1" s="10" customFormat="1" ht="45" spans="1:16">
+      <c r="A1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="13">
-        <v>45748</v>
-      </c>
-      <c r="B2" s="13">
-        <v>47211</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="8">
+      <c r="N1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="12">
+        <v>2</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="13">
+        <v>180000000</v>
+      </c>
+      <c r="H2" s="13">
+        <v>180000000</v>
+      </c>
+      <c r="I2" s="14">
+        <v>50000000</v>
+      </c>
+      <c r="J2" s="15">
+        <f>MAX(0,G2+H2-I2)</f>
+        <v>310000000</v>
+      </c>
+      <c r="K2" s="12">
+        <f>YEAR(D2)-IF(MONTH(D2)&lt;4,1,0)-YEAR(C2)+IF(MONTH(C2)&lt;4,1,0)+1</f>
+        <v>4</v>
+      </c>
+      <c r="L2" s="12">
+        <v>2</v>
+      </c>
+      <c r="M2" s="16">
+        <f>IF(E2=2,0.005,IF(K2&lt;=4,0.015,0.01))</f>
+        <v>0.005</v>
+      </c>
+      <c r="N2" s="17">
+        <f>IF(OR(F2="NPA",F2="CLOSE"),0,J2*M2)</f>
+        <v>1550000</v>
+      </c>
+      <c r="O2" s="17">
+        <f>IF(OR(F2="NPA",F2="CLOSE"),0,N2*L2)</f>
+        <v>3100000</v>
+      </c>
+      <c r="P2" s="17">
+        <f>N2+O2</f>
+        <v>4650000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="12">
         <v>1</v>
       </c>
-      <c r="F2" s="14">
-        <v>1000012.79</v>
-      </c>
-      <c r="G2" s="14">
-        <v>1001.79</v>
-      </c>
-      <c r="H2" s="8">
-        <v>500</v>
-      </c>
-      <c r="I2" s="8">
-        <f>F2+G2</f>
-        <v>1001014.58</v>
-      </c>
-      <c r="J2" s="8">
-        <f>I2-H2</f>
-        <v>1000514.58</v>
-      </c>
-      <c r="K2" s="8">
+      <c r="F3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="13">
+        <v>1000000000</v>
+      </c>
+      <c r="H3" s="13">
+        <v>1000000000</v>
+      </c>
+      <c r="I3" s="14">
+        <v>50000000</v>
+      </c>
+      <c r="J3" s="15">
+        <f>MAX(0,G3+H3-I3)</f>
+        <v>1950000000</v>
+      </c>
+      <c r="K3" s="12">
+        <f>YEAR(D3)-IF(MONTH(D3)&lt;4,1,0)-YEAR(C3)+IF(MONTH(C3)&lt;4,1,0)+1</f>
         <v>4</v>
       </c>
-      <c r="L2" s="8">
-        <f>IF(E2=1,IF(K2&lt;=3,0.015,0.01),0.005)</f>
-        <v>0.01</v>
-      </c>
-      <c r="M2" s="8">
-        <f>IF(AND(C2="NPA",D2="STANDARD"),J2*L2*2,IF(D2="STANDARD",J2*L2,0))</f>
-        <v>10005.1458</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="13">
-        <v>45748</v>
-      </c>
-      <c r="B3" s="13">
-        <v>47211</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="8">
+      <c r="L3" s="12">
+        <v>2</v>
+      </c>
+      <c r="M3" s="16">
+        <f>IF(E3=2,0.005,IF(K3&lt;=4,0.015,0.01))</f>
+        <v>0.015</v>
+      </c>
+      <c r="N3" s="17">
+        <f>IF(OR(F3="NPA",F3="CLOSE"),0,J3*M3)</f>
+        <v>29250000</v>
+      </c>
+      <c r="O3" s="17">
+        <f>IF(OR(F3="NPA",F3="CLOSE"),0,N3*L3)</f>
+        <v>58500000</v>
+      </c>
+      <c r="P3" s="17">
+        <f>N3+O3</f>
+        <v>87750000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F3" s="15">
-        <v>1000043.02</v>
-      </c>
-      <c r="G3" s="15">
-        <v>100043.02</v>
-      </c>
-      <c r="H3" s="8">
-        <v>500</v>
-      </c>
-      <c r="I3" s="8">
-        <f>F3+G3</f>
-        <v>1100086.04</v>
-      </c>
-      <c r="J3" s="8">
-        <f>I3-H3</f>
-        <v>1099586.04</v>
-      </c>
-      <c r="K3" s="8">
+      <c r="F4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="13">
+        <v>1000000000</v>
+      </c>
+      <c r="H4" s="13">
+        <v>1000000000</v>
+      </c>
+      <c r="I4" s="14">
+        <v>50000000</v>
+      </c>
+      <c r="J4" s="15">
+        <f>MAX(0,G4+H4-I4)</f>
+        <v>1950000000</v>
+      </c>
+      <c r="K4" s="12">
+        <f>YEAR(D4)-IF(MONTH(D4)&lt;4,1,0)-YEAR(C4)+IF(MONTH(C4)&lt;4,1,0)+1</f>
         <v>4</v>
       </c>
-      <c r="L3" s="8">
-        <f>IF(E3=1,IF(K3&lt;=3,0.015,0.01),0.005)</f>
-        <v>0.01</v>
-      </c>
-      <c r="M3" s="8">
-        <f>IF(AND(C3="NPA",D3="STANDARD"),J3*L3*2,IF(D3="STANDARD",J3*L3,0))</f>
-        <v>10995.8604</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="13">
-        <v>45748</v>
-      </c>
-      <c r="B4" s="13">
-        <v>47211</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="8">
+      <c r="L4" s="12">
         <v>2</v>
       </c>
-      <c r="F4" s="15">
-        <v>200300.33</v>
-      </c>
-      <c r="G4" s="15">
-        <v>200200.33</v>
-      </c>
-      <c r="H4" s="8">
-        <v>500</v>
-      </c>
-      <c r="I4" s="8">
-        <f>F4+G4</f>
-        <v>400500.66</v>
-      </c>
-      <c r="J4" s="8">
-        <f>I4-H4</f>
-        <v>400000.66</v>
-      </c>
-      <c r="K4" s="8">
-        <v>4</v>
-      </c>
-      <c r="L4" s="8">
-        <f>IF(E4=1,IF(K4&lt;=3,0.015,0.01),0.005)</f>
-        <v>0.005</v>
-      </c>
-      <c r="M4" s="8">
-        <f>IF(AND(C4="NPA",D4="STANDARD"),J4*L4*2,IF(D4="STANDARD",J4*L4,0))</f>
-        <v>2000.0033</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="13">
-        <v>45748</v>
-      </c>
-      <c r="B5" s="13">
-        <v>47211</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="8">
-        <v>2</v>
-      </c>
-      <c r="F5" s="15">
-        <v>20010.65</v>
-      </c>
-      <c r="G5" s="15">
-        <v>20300.65</v>
-      </c>
-      <c r="H5" s="8">
-        <v>500</v>
-      </c>
-      <c r="I5" s="8">
-        <f>F5+G5</f>
-        <v>40311.3</v>
-      </c>
-      <c r="J5" s="8">
-        <f>I5-H5</f>
-        <v>39811.3</v>
-      </c>
-      <c r="L5" s="8">
-        <f>IF(E5=1,IF(K5&lt;=3,0.015,0.01),0.005)</f>
-        <v>0.005</v>
-      </c>
-      <c r="M5" s="8">
-        <f>IF(AND(C5="NPA",D5="STANDARD"),J5*L5*2,IF(D5="STANDARD",J5*L5,0))</f>
-        <v>199.0565</v>
+      <c r="M4" s="16">
+        <f>IF(E4=2,0.005,IF(K4&lt;=4,0.015,0.01))</f>
+        <v>0.015</v>
+      </c>
+      <c r="N4" s="17">
+        <f>IF(OR(F4="NPA",F4="CLOSE"),0,J4*M4)</f>
+        <v>29250000</v>
+      </c>
+      <c r="O4" s="17">
+        <f>IF(OR(F4="NPA",F4="CLOSE"),0,N4*L4)</f>
+        <v>58500000</v>
+      </c>
+      <c r="P4" s="17">
+        <f>N4+O4</f>
+        <v>87750000</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="F2:F4">
+      <formula1>"STANDARD,NPA,CLOSE"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" sqref="L2:L4">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -2699,83 +2747,83 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="17.4285714285714" style="8" customWidth="1"/>
-    <col min="2" max="2" width="18" style="8" customWidth="1"/>
-    <col min="3" max="3" width="15.5714285714286" style="8" customWidth="1"/>
-    <col min="4" max="4" width="29.4285714285714" style="8" customWidth="1"/>
-    <col min="5" max="5" width="17.7142857142857" style="8" customWidth="1"/>
-    <col min="6" max="6" width="19.5714285714286" style="8" customWidth="1"/>
-    <col min="7" max="7" width="19.8571428571429" style="8" customWidth="1"/>
-    <col min="8" max="8" width="16.2857142857143" style="8" customWidth="1"/>
-    <col min="9" max="9" width="10.8571428571429" style="8" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="17.4285714285714" style="7" customWidth="1"/>
+    <col min="2" max="2" width="18" style="7" customWidth="1"/>
+    <col min="3" max="3" width="15.5714285714286" style="7" customWidth="1"/>
+    <col min="4" max="4" width="29.4285714285714" style="7" customWidth="1"/>
+    <col min="5" max="5" width="17.7142857142857" style="7" customWidth="1"/>
+    <col min="6" max="6" width="19.5714285714286" style="7" customWidth="1"/>
+    <col min="7" max="7" width="19.8571428571429" style="7" customWidth="1"/>
+    <col min="8" max="8" width="16.2857142857143" style="7" customWidth="1"/>
+    <col min="9" max="9" width="10.8571428571429" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" spans="1:9">
-      <c r="A1" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" s="8" customFormat="1" spans="1:9">
-      <c r="A2" s="10">
-        <v>46853</v>
-      </c>
-      <c r="B2" s="10">
+    <row r="1" s="7" customFormat="1" spans="1:9">
+      <c r="A1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" s="7" customFormat="1" spans="1:9">
+      <c r="A2" s="9">
+        <v>47587</v>
+      </c>
+      <c r="B2" s="9">
         <f>DATE(YEAR(A2)-(MONTH(A2)&lt;4),3,31)</f>
-        <v>46843</v>
-      </c>
-      <c r="C2" s="10">
-        <v>46783</v>
-      </c>
-      <c r="D2" s="10">
+        <v>47573</v>
+      </c>
+      <c r="C2" s="9">
+        <v>47452</v>
+      </c>
+      <c r="D2" s="9">
         <f>A2-180</f>
-        <v>46673</v>
-      </c>
-      <c r="E2" s="10">
+        <v>47407</v>
+      </c>
+      <c r="E2" s="9">
         <f>DATE(YEAR(A2)-1-(MONTH(A2)&lt;4),4,1)</f>
-        <v>46478</v>
-      </c>
-      <c r="F2" s="10">
+        <v>47209</v>
+      </c>
+      <c r="F2" s="9">
         <f>MAX(D2,E2)</f>
-        <v>46673</v>
-      </c>
-      <c r="G2" s="10">
+        <v>47407</v>
+      </c>
+      <c r="G2" s="9">
         <f>B2</f>
-        <v>46843</v>
-      </c>
-      <c r="H2" s="9">
+        <v>47573</v>
+      </c>
+      <c r="H2" s="8">
         <f>A2-C2</f>
-        <v>70</v>
-      </c>
-      <c r="I2" s="9" t="str">
+        <v>135</v>
+      </c>
+      <c r="I2" s="8" t="str">
         <f>IF(AND(C2&gt;=F2,C2&lt;=G2),"Valid","Invalid")</f>
         <v>Valid</v>
       </c>
@@ -2788,35 +2836,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="13.2857142857143" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="7">
-        <v>47027</v>
-      </c>
-      <c r="B1" s="7">
-        <v>47208</v>
-      </c>
-      <c r="D1">
-        <f>B1-A1</f>
-        <v>181</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:P21"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
@@ -2831,63 +2851,63 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D2" s="2">
         <v>47027</v>
@@ -2935,13 +2955,13 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D3" s="2">
         <v>47027</v>
@@ -2989,13 +3009,13 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D4" s="2">
         <v>47027</v>
@@ -3043,13 +3063,13 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D5" s="2">
         <v>47027</v>
@@ -3097,13 +3117,13 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2">
         <v>47027</v>
@@ -3151,13 +3171,13 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2">
         <v>47027</v>
@@ -3205,13 +3225,13 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D8" s="2">
         <v>47027</v>
@@ -3259,13 +3279,13 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D9" s="2">
         <v>47027</v>
@@ -3313,13 +3333,13 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D10" s="2">
         <v>47027</v>
@@ -3367,13 +3387,13 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D11" s="2">
         <v>47027</v>
@@ -3421,13 +3441,13 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D12" s="2">
         <v>47027</v>
@@ -3475,13 +3495,13 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D13" s="2">
         <v>47027</v>
@@ -3529,13 +3549,13 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D14" s="2">
         <v>47027</v>
@@ -3583,13 +3603,13 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D15" s="2">
         <v>47027</v>
@@ -3637,13 +3657,13 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D16" s="2">
         <v>47027</v>
@@ -3691,13 +3711,13 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D17" s="2">
         <v>47027</v>
@@ -3745,13 +3765,13 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D18" s="2">
         <v>47027</v>
@@ -3799,13 +3819,13 @@
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D19" s="2">
         <v>47027</v>
@@ -3853,13 +3873,13 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="1" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D20" s="2">
         <v>47027</v>
@@ -3907,13 +3927,13 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D21" s="2">
         <v>47027</v>
